--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-01-2026.xlsx
@@ -1866,7 +1866,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£82.06</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.planetinsulation.co.uk/products/celotex-pir-tb-ga-xr?variant=42844828696813</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.50</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
